--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487572_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487572_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7685</v>
+        <v>7.0424</v>
       </c>
       <c r="E2" t="n">
-        <v>7.865</v>
+        <v>7.9409</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0965</v>
+        <v>-0.8985</v>
       </c>
       <c r="G2" t="n">
         <v>2.462</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>1.538</v>
+        <v>0.8119</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1141</v>
+        <v>-0.0382</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6521</v>
+        <v>0.8502</v>
       </c>
       <c r="V2" t="n">
         <v>2.5934</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.013</v>
+        <v>3.7732</v>
       </c>
       <c r="E3" t="n">
-        <v>7.71</v>
+        <v>7.096</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.6971</v>
+        <v>-3.3228</v>
       </c>
       <c r="G3" t="n">
         <v>2.023</v>
@@ -688,13 +688,13 @@
         <v>0.1958</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2607</v>
+        <v>0.0209</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8057</v>
+        <v>0.1917</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5451</v>
+        <v>-0.1708</v>
       </c>
       <c r="V3" t="n">
         <v>2.7086</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5908</v>
+        <v>0.1118</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2926</v>
+        <v>2.8403</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.7018</v>
+        <v>-2.7285</v>
       </c>
       <c r="G4" t="n">
         <v>-2.6086</v>
@@ -766,13 +766,13 @@
         <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.825</v>
+        <v>0.346</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8828</v>
+        <v>0.4305</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0578</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>2.7662</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1964</v>
+        <v>-0.0509</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0165</v>
+        <v>0.1023</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1798</v>
+        <v>-0.1531</v>
       </c>
       <c r="G5" t="n">
         <v>0.2787</v>
@@ -844,13 +844,13 @@
         <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2792</v>
+        <v>-0.1337</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3564</v>
+        <v>-0.2376</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0772</v>
+        <v>0.104</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1995</v>
+        <v>-0.8189</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1866</v>
+        <v>-0.3874</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3861</v>
+        <v>-0.4315</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8518</v>
+        <v>-1.7343</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8356</v>
+        <v>0.5189</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.6874</v>
+        <v>-2.2532</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3731</v>
+        <v>-0.1927</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8533</v>
+        <v>0.4491</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4802</v>
+        <v>-0.6418</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.2249</v>
+        <v>-1.5416</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0176</v>
+        <v>0.0698</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.2073</v>
+        <v>-1.6114</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7834</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1543</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.956</v>
+        <v>0.132</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1911</v>
+        <v>-0.1947</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7649</v>
+        <v>0.3267</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.159</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5507</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2004</v>
+        <v>-0.9868</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6085</v>
+        <v>1.9984</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5919</v>
+        <v>-2.9852</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7343</v>
+        <v>-0.8518</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5189</v>
+        <v>2.8356</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2532</v>
+        <v>-3.6874</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1927</v>
+        <v>3.3731</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4491</v>
+        <v>3.8533</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6418</v>
+        <v>-0.4802</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5416</v>
+        <v>-4.2249</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0698</v>
+        <v>-1.0176</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6114</v>
+        <v>-3.2073</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7834</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7834</v>
+        <v>2.1543</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2495</v>
+        <v>-0.7433</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4158</v>
+        <v>-0.3794</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1663</v>
+        <v>-0.3639</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.159</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.531</v>
+        <v>-1.0715</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4417</v>
+        <v>2.1151</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9727</v>
+        <v>-3.1865</v>
       </c>
       <c r="G8" t="n">
         <v>0.7743</v>
@@ -1078,13 +1078,13 @@
         <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.189</v>
+        <v>0.2705</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6005</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4115</v>
+        <v>0.1976</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9412</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MELGAR ZORITA</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2348</v>
+        <v>-1.7941</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9184</v>
+        <v>0.2694</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3164</v>
+        <v>-2.0634</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0746</v>
+        <v>-1.2211</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.115</v>
+        <v>1.4311</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0404</v>
+        <v>-2.6522</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0608</v>
+        <v>1.808</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0204</v>
+        <v>2.4498</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0404</v>
+        <v>-0.6418</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1354</v>
+        <v>-3.029</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1354</v>
+        <v>-1.0187</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-2.0104</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0356</v>
+        <v>-0.1617</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>0.1641</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0356</v>
+        <v>-0.3258</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>-0.9988</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7235</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>M. MELGAR ZORITA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3743</v>
+        <v>-1.9767</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.7137</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2773</v>
+        <v>-1.2629</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2211</v>
+        <v>-0.0746</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4311</v>
+        <v>-0.115</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6522</v>
+        <v>0.0404</v>
       </c>
       <c r="J10" t="n">
-        <v>1.808</v>
+        <v>0.0608</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4498</v>
+        <v>0.0204</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6418</v>
+        <v>0.0404</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.029</v>
+        <v>-0.1354</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0187</v>
+        <v>-0.1354</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0104</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5875</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5668</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.742</v>
+        <v>0.2938</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2023</v>
+        <v>0.2047</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5397</v>
+        <v>0.0891</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9988</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7235</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9651</v>
+        <v>-2.667</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1601</v>
+        <v>-1.6749</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.992</v>
       </c>
       <c r="G11" t="n">
         <v>-3.272</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0535</v>
+        <v>0.3516</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4993</v>
+        <v>-0.0141</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5528</v>
+        <v>0.3657</v>
       </c>
       <c r="V11" t="n">
         <v>0.0576</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6708000000000012</v>
+        <v>1.561500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>18.6953</v>
+        <v>19.5864</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.0245</v>
+        <v>-18.0244</v>
       </c>
       <c r="G12" t="n">
         <v>-4.224399999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>9.868800000000002</v>
+        <v>9.8688</v>
       </c>
       <c r="I12" t="n">
         <v>-14.0933</v>
@@ -1381,7 +1381,7 @@
         <v>-18.7134</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9792000000000003</v>
+        <v>-0.9791999999999998</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.7093</v>
@@ -1390,16 +1390,16 @@
         <v>12.73</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2971</v>
+        <v>1.188</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6910000000000001</v>
+        <v>0.1999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9879999999999999</v>
+        <v>0.9883</v>
       </c>
       <c r="V12" t="n">
-        <v>5.577499999999999</v>
+        <v>5.5775</v>
       </c>
       <c r="W12" t="n">
         <v>11.4876</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2999</v>
+        <v>4.501</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4086</v>
+        <v>3.8179</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8914</v>
+        <v>0.6831</v>
       </c>
       <c r="G13" t="n">
         <v>0.0591</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3215</v>
+        <v>0.5226</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7722</v>
+        <v>-0.3629</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0937</v>
+        <v>0.8854</v>
       </c>
       <c r="V13" t="n">
         <v>2.5484</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0773</v>
+        <v>3.0478</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4585</v>
+        <v>4.0492</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3813</v>
+        <v>-1.0015</v>
       </c>
       <c r="G14" t="n">
         <v>1.7164</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4565</v>
+        <v>0.427</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2711</v>
+        <v>-0.1382</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1854</v>
+        <v>0.5652</v>
       </c>
       <c r="V14" t="n">
         <v>1.492</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1943</v>
+        <v>1.9952</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1924</v>
+        <v>3.9877</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9981</v>
+        <v>-1.9925</v>
       </c>
       <c r="G15" t="n">
         <v>1.4294</v>
@@ -1624,13 +1624,13 @@
         <v>1.7626</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8075</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3611</v>
+        <v>0.1564</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4464</v>
+        <v>0.452</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8260999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8005</v>
+        <v>1.4514</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8763</v>
+        <v>4.3879</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0758</v>
+        <v>-2.9365</v>
       </c>
       <c r="G16" t="n">
         <v>2.9624</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6284</v>
+        <v>0.0225</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9504</v>
+        <v>-0.4388</v>
       </c>
       <c r="U16" t="n">
-        <v>0.322</v>
+        <v>0.4613</v>
       </c>
       <c r="V16" t="n">
         <v>-2.7086</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6417</v>
+        <v>0.7487</v>
       </c>
       <c r="E17" t="n">
         <v>1.764</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1222</v>
+        <v>-1.0153</v>
       </c>
       <c r="G17" t="n">
         <v>2.2737</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.261</v>
+        <v>-0.1541</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0828</v>
+        <v>0.0241</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1399</v>
+        <v>0.1461</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3037</v>
+        <v>3.0201</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.4437</v>
+        <v>-2.874</v>
       </c>
       <c r="G18" t="n">
         <v>1.5629</v>
@@ -1858,13 +1858,13 @@
         <v>2.1543</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1693</v>
+        <v>0.1167</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9745</v>
+        <v>-0.2582</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1948</v>
+        <v>0.3749</v>
       </c>
       <c r="V18" t="n">
         <v>-2.7086</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1632</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9526</v>
+        <v>-0.8502</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2106</v>
+        <v>-0.0474</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5941</v>
@@ -1936,13 +1936,13 @@
         <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3145</v>
+        <v>-0.049</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0594</v>
+        <v>0.0429</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2551</v>
+        <v>-0.0919</v>
       </c>
       <c r="V19" t="n">
         <v>0.3329</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8982</v>
+        <v>-3.5037</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9398</v>
+        <v>-0.7352</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9584</v>
+        <v>-2.7685</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4423</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5343</v>
+        <v>-0.1397</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3211</v>
+        <v>-0.1165</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2131</v>
+        <v>-0.0232</v>
       </c>
       <c r="V21" t="n">
         <v>0.0576</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2665</v>
+        <v>-4.8963</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-1.4169</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.18</v>
+        <v>-3.4794</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7431</v>
@@ -2170,13 +2170,13 @@
         <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>1.025</v>
+        <v>0.3952</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6356</v>
+        <v>0.3052</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6106</v>
+        <v>0.09</v>
       </c>
       <c r="V22" t="n">
         <v>-2.5484</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6707000000000001</v>
+        <v>1.3759</v>
       </c>
       <c r="E23" t="n">
-        <v>18.0246</v>
+        <v>18.0245</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.6953</v>
+        <v>-16.6486</v>
       </c>
       <c r="G23" t="n">
         <v>4.224400000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.7092</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2969999999999999</v>
+        <v>1.7496</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9880000000000002</v>
+        <v>-0.9883000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6910999999999998</v>
+        <v>2.7378</v>
       </c>
       <c r="V23" t="n">
         <v>-5.5774</v>
